--- a/python/Py Quant Trading Practise/Pct Pattern.xlsx
+++ b/python/Py Quant Trading Practise/Pct Pattern.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BaiduNetdiskDownload\Quants\python\Py Quant Trading Practise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2F4392-6FC6-4AE4-990D-7D616AE64008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0755EBDC-E695-4326-A3F6-8371F6B19AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12180" yWindow="4068" windowWidth="16320" windowHeight="8748" tabRatio="686" firstSheet="2" activeTab="7" xr2:uid="{B0460CFB-DAA0-4C97-B704-D5C95F6EFBEE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="686" firstSheet="1" activeTab="9" xr2:uid="{B0460CFB-DAA0-4C97-B704-D5C95F6EFBEE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet name="Sheet2" sheetId="6" r:id="rId6"/>
     <sheet name="ma category" sheetId="7" r:id="rId7"/>
     <sheet name="mv stage2" sheetId="8" r:id="rId8"/>
+    <sheet name="双周期" sheetId="9" r:id="rId9"/>
+    <sheet name="Peak-valleyru" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="218">
   <si>
     <t>大跌</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -745,6 +747,94 @@
   </si>
   <si>
     <t>0.95, 1.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>放量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mv1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mv2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mv3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v&gt;mv1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mv1 &gt; mv2*1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mv2 &gt; mv3*1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>放巨量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;mv1*1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>m60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>live</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PV1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZPCT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PV2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PV3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用于发现大阴大阳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用于指定空头区域,多头区域, 突破区域，破位区域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -752,7 +842,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -783,6 +873,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -806,7 +904,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -817,6 +915,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1252,6 +1353,66 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6642237-6FD7-4315-A92C-2F790FACAF58}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="32.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B2">
+        <v>2E-3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEBAB265-5B64-4869-8D9D-3FA57F95146D}">
   <dimension ref="A1:D4"/>
@@ -1312,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A6B9F04-9A9B-4EC8-AEA6-95032E366215}">
-  <dimension ref="B1:I19"/>
+  <dimension ref="B1:I23"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.88671875" customWidth="1"/>
@@ -1320,9 +1481,9 @@
     <col min="3" max="3" width="5.6640625" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" customWidth="1"/>
+    <col min="8" max="8" width="5.109375" customWidth="1"/>
     <col min="9" max="9" width="22.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1827,6 +1988,39 @@
       <c r="I19" t="str">
         <f>"[" &amp;H19&amp;","&amp;""""&amp;E19&amp;""""&amp;"]]"</f>
         <v>[18,"空转多反弹"]]</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>197</v>
+      </c>
+      <c r="F21" t="s">
+        <v>198</v>
+      </c>
+      <c r="G21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>203</v>
+      </c>
+      <c r="E22" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>196</v>
+      </c>
+      <c r="E23" t="s">
+        <v>200</v>
+      </c>
+      <c r="F23" t="s">
+        <v>201</v>
+      </c>
+      <c r="G23" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2982,4 +3176,167 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{763F5D75-A53B-49C0-A677-BDD2E12B0C06}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <f>B2/3</f>
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <f>B2/6</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C8" si="0">B3/3</f>
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D8" si="1">B3/6</f>
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <f>B3/12</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E8" si="2">B4/12</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>48</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>96</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f>B6*2</f>
+        <v>192</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <f>B7*2</f>
+        <v>384</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/python/Py Quant Trading Practise/Pct Pattern.xlsx
+++ b/python/Py Quant Trading Practise/Pct Pattern.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BaiduNetdiskDownload\Quants\python\Py Quant Trading Practise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0755EBDC-E695-4326-A3F6-8371F6B19AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7F73C0-1EDF-4FCF-B3D6-D2C3401E0BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="686" firstSheet="1" activeTab="9" xr2:uid="{B0460CFB-DAA0-4C97-B704-D5C95F6EFBEE}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="ma category" sheetId="7" r:id="rId7"/>
     <sheet name="mv stage2" sheetId="8" r:id="rId8"/>
     <sheet name="双周期" sheetId="9" r:id="rId9"/>
-    <sheet name="Peak-valleyru" sheetId="10" r:id="rId10"/>
+    <sheet name="Peak-valley" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="223">
   <si>
     <t>大跌</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -835,6 +835,26 @@
   </si>
   <si>
     <t>用于指定空头区域,多头区域, 突破区域，破位区域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>case1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peak1,2,3 都在上面，说明有压力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未到前面压力，peak1开始反转</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配合量能，如果mv_stage=1, 则是缩量，大概率会下跌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>震荡底部启动趋势</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -904,7 +924,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -919,6 +939,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -935,6 +958,143 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>320040</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>366081</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>137296</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{280BBDBD-37C6-06B5-4FD8-693CB1A28C2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6987540" y="845820"/>
+          <a:ext cx="3703641" cy="1569856"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>130015</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>53595</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55C4A341-08A1-3F03-380E-D7D22EFE9E89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6804660" y="2720340"/>
+          <a:ext cx="5479255" cy="2941575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>533710</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>182</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11BB417D-5D18-D0E7-4ED4-B16097ABB18B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6667500" y="6134100"/>
+          <a:ext cx="3581710" cy="2103302"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1355,13 +1515,14 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6642237-6FD7-4315-A92C-2F790FACAF58}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="32.109375" customWidth="1"/>
+    <col min="4" max="4" width="38.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>212</v>
       </c>
@@ -1369,7 +1530,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>211</v>
       </c>
@@ -1380,7 +1541,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>213</v>
       </c>
@@ -1388,7 +1549,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>214</v>
       </c>
@@ -1399,17 +1560,40 @@
         <v>217</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>209</v>
       </c>
       <c r="B7" t="s">
         <v>210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>220</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
